--- a/examples/evm.xlsx
+++ b/examples/evm.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +29,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,11 +82,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -59,6 +109,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -133,6 +191,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The month the row reports: 2026-01, 1/31/2026 or 1, 2, 3.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Optional label; with it every account is analysed as well as the total.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Budgeted cost of work scheduled in the period (not cumulative).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Budgeted cost of work performed in the period.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Actual cost of work performed in the period.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Optional: the contractor's estimate at completion as reported.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,10 +519,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -436,1921 +535,2123 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Control Account</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Planned Value (BCWS)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Earned Value (BCWP)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Actual Cost (ACWP)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Contractor EAC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>18.9</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>14.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
         <v>54.9</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>24.8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>25.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>9030.799999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>51.5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>56.7</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>9061.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>142.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>77.3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>84.7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>9092.299999999999</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>189.6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>112.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>127.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>9123.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>236.8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>161.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>177.2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>9153.799999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
         <v>283</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>192.8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>216.4</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>9184.6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>326.9</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>230.6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>272</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>9215.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
         <v>367.6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>246.4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>274.5</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>9246.200000000001</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>404.2</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>275.3</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="6" t="n">
         <v>342.2</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>9276.9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>435.9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>290.8</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="6" t="n">
         <v>329.5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>9307.700000000001</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>462.1</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>319.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>366.1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="6" t="n">
         <v>9338.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>482.2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="6" t="n">
         <v>383.4</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>388.1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="6" t="n">
         <v>9369.200000000001</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>495.8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="6" t="n">
         <v>359.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="6" t="n">
         <v>353.6</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="6" t="n">
         <v>9400</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>502.7</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
         <v>502.7</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>495.8</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>482.2</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
         <v>462.1</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>435.9</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
         <v>404.2</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>367.6</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
         <v>326.9</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>2027-09</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>283</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
         <v>236.8</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>2027-11</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>189.6</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
         <v>142.5</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
         <v>54.9</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>2028-03</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1.1 Air vehicle</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Air vehicle</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
         <v>18.9</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
         <v>8.4</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>6.8</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="6" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
         <v>24.4</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="6" t="n">
         <v>9.1</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>10.3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="6" t="n">
         <v>4026.9</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
         <v>43.1</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="6" t="n">
         <v>4053.8</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
         <v>63.3</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="6" t="n">
         <v>29.6</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="6" t="n">
         <v>4080.8</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
         <v>84.3</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="6" t="n">
         <v>37.3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="6" t="n">
         <v>45.6</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="6" t="n">
         <v>4107.7</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
         <v>105.3</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="6" t="n">
         <v>53.2</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="6" t="n">
         <v>4134.6</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
         <v>125.8</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="6" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="6" t="n">
         <v>4161.5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
         <v>145.3</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="6" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>84.3</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="6" t="n">
         <v>4188.5</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
         <v>163.4</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="6" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>107.7</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="6" t="n">
         <v>4215.4</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
         <v>179.6</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="6" t="n">
         <v>137.4</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="6" t="n">
         <v>173</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="6" t="n">
         <v>4242.3</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
         <v>193.7</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="6" t="n">
         <v>180.1</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="6" t="n">
         <v>185.2</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="6" t="n">
         <v>4269.2</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
         <v>205.4</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="6" t="n">
         <v>198.1</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="6" t="n">
         <v>4296.2</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
         <v>214.3</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="6" t="n">
         <v>169.4</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="6" t="n">
         <v>183.8</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="6" t="n">
         <v>4323.1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
         <v>220.4</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="6" t="n">
         <v>158.5</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="6" t="n">
         <v>184.4</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="6" t="n">
         <v>4350</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
         <v>223.4</v>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
         <v>223.4</v>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
         <v>220.4</v>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
         <v>214.3</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
         <v>205.4</v>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
         <v>193.7</v>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
         <v>179.6</v>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
         <v>163.4</v>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
         <v>145.3</v>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>2027-09</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
         <v>125.8</v>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
         <v>105.3</v>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>2027-11</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
         <v>84.3</v>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
         <v>63.3</v>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
         <v>43.1</v>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
         <v>24.4</v>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>2028-03</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1.2 Software</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
         <v>8.4</v>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="6" t="n">
         <v>4.9</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="6" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="6" t="n">
         <v>16.9</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="6" t="n">
         <v>18.3</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="6" t="n">
         <v>2503.8</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="6" t="n">
         <v>24.7</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="6" t="n">
         <v>28.4</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="6" t="n">
         <v>2507.7</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
         <v>39.6</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="6" t="n">
         <v>32.1</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="6" t="n">
         <v>39.3</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="6" t="n">
         <v>2511.5</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
         <v>52.7</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="6" t="n">
         <v>38.3</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="6" t="n">
         <v>39.6</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="6" t="n">
         <v>2515.4</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
         <v>65.8</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="6" t="n">
         <v>46.9</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="6" t="n">
         <v>48.1</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="6" t="n">
         <v>2519.2</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="6" t="n">
         <v>49.3</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="6" t="n">
         <v>50.6</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="6" t="n">
         <v>2523.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
         <v>90.8</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="6" t="n">
         <v>49.5</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="6" t="n">
         <v>54.1</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="6" t="n">
         <v>2526.9</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
         <v>102.1</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="6" t="n">
         <v>95.2</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="6" t="n">
         <v>106.5</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="6" t="n">
         <v>2530.8</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
         <v>112.3</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="6" t="n">
         <v>117.3</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="6" t="n">
         <v>123.2</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="6" t="n">
         <v>2534.6</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
         <v>121.1</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="6" t="n">
         <v>2538.5</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
         <v>128.4</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="6" t="n">
         <v>143.5</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="6" t="n">
         <v>156.5</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="6" t="n">
         <v>2542.3</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
         <v>133.9</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="6" t="n">
         <v>186.2</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="6" t="n">
         <v>2546.2</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
         <v>137.7</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="6" t="n">
         <v>152.9</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="6" t="n">
         <v>161.1</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="6" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
         <v>139.6</v>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
         <v>139.6</v>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="D77" s="6" t="inlineStr"/>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
         <v>137.7</v>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
         <v>133.9</v>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr"/>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
         <v>128.4</v>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
         <v>121.1</v>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="D81" s="6" t="inlineStr"/>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
         <v>112.3</v>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="D82" s="6" t="inlineStr"/>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
         <v>102.1</v>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
         <v>90.8</v>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>2027-09</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="D85" s="6" t="inlineStr"/>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
         <v>65.8</v>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>2027-11</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
         <v>52.7</v>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="D87" s="6" t="inlineStr"/>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
         <v>39.6</v>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr"/>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>2028-03</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1.3 Systems engineering</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Systems engineering</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="6" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="F105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="F107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+      <c r="E111" s="6" t="n"/>
+      <c r="F111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2358,156 +2659,223 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>How to fill in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Yours to fill in. The example rows are there to show the layout: type over them, and add more rows in the yellow space below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Dark blue heading</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A column that must be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Light blue heading</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>An optional column: leave it blank if it doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Grey cells</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Labels: leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Hover over a heading</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A note says what goes in that column, in what units, with an example. A small arrow in a cell means a drop-down list of the allowed answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Column or topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>What to put there</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>What this workbook is</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>The input for `ce-core evm --data my_evm.xlsx`. The Data sheet holds an invented example program so the layout is plain: replace it with yours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>One row per</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Reporting period, per control account. Without a Control Account column, one row per period for the whole program.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>The month the row reports: 2026-01, 1/31/2026 or a number 1, 2, 3 ... all work. Periods sort by date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Control Account</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Optional. Any label. With it, every account is analysed as well as the program total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Planned Value (BCWS)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>What the baseline planned to be done in that period. Fill it in for every period to the end of the plan, including the future.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Earned Value (BCWP)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The budgeted value of the work actually done in that period. Leave blank after the latest (status) period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Actual Cost (ACWP)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>What that work actually cost in that period. Leave blank after the status period.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Contractor EAC</t>
+          <t>What this workbook is</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Optional. The contractor's estimate at completion, if reported.</t>
+          <t>The input for `ce-core evm --data my_evm.xlsx`. The Data sheet holds an invented example program so the layout is plain: replace it with yours.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Per period, not to date</t>
+          <t>One row per</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Each value is that period's own amount. For cumulative to-date values instead, run with --cumulative.</t>
+          <t>Reporting period, per control account. Without a Control Account column, one row per period for the whole program.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Any one currency unit throughout: dollars, thousands or millions. Say which with --units thousands (or dollars, millions) for the labels; nothing is converted.</t>
+          <t>The month the row reports: 2026-01, 1/31/2026 or a number 1, 2, 3 ... all work. Periods sort by date.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Other column names</t>
+          <t>Control Account</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>PV, EV, AC, 'Planned Value', 'Month', 'WBS' and similar are recognised too, so an export from another tool may read as it is.</t>
+          <t>Optional. Any label. With it, every account is analysed as well as the program total.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Planned Value (BCWS)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>What the baseline planned to be done in that period. Fill it in for every period to the end of the plan, including the future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Earned Value (BCWP)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The budgeted value of the work actually done in that period. Leave blank after the latest (status) period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Actual Cost (ACWP)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>What that work actually cost in that period. Leave blank after the status period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Contractor EAC</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Optional. The contractor's estimate at completion, if reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Per period, not to date</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Each value is that period's own amount. For cumulative to-date values instead, run with --cumulative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Any one currency unit throughout: dollars, thousands or millions. Say which with --units thousands (or dollars, millions) for the labels; nothing is converted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Other column names</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>PV, EV, AC, 'Planned Value', 'Month', 'WBS' and similar are recognised too, so an export from another tool may read as it is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>From an IPMDAR</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>No need for this workbook: `ce-core evm --ipmdar the_delivery.zip`.</t>
         </is>
